--- a/results/training.xlsx
+++ b/results/training.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\projects\RF_DCOPF\results\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDDD66A-F882-4540-A65B-0192E8099568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="training_performance_percentage" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,8 +24,61 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
+  <si>
+    <t>pglib_opf_case73_ieee_rts</t>
+  </si>
+  <si>
+    <t>pglib_opf_case89_pegase</t>
+  </si>
+  <si>
+    <t>pglib_opf_case118_ieee</t>
+  </si>
+  <si>
+    <t>pglib_opf_case162_ieee_dtc</t>
+  </si>
+  <si>
+    <t>pglib_opf_case179_goc</t>
+  </si>
+  <si>
+    <t>pglib_opf_case200_activ</t>
+  </si>
+  <si>
+    <t>pglib_opf_case240_pserc</t>
+  </si>
+  <si>
+    <t>pglib_opf_case300_ieee</t>
+  </si>
+  <si>
+    <t>pglib_opf_case500_goc</t>
+  </si>
+  <si>
+    <t>pglib_opf_case588_sdet</t>
+  </si>
+  <si>
+    <t>pglib_opf_case197_snem</t>
+  </si>
+  <si>
+    <t>rf</t>
+  </si>
+  <si>
+    <t>ada</t>
+  </si>
+  <si>
+    <t>xgb</t>
+  </si>
+  <si>
+    <t>knn</t>
+  </si>
+  <si>
+    <t>mlp</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -49,8 +108,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +393,159 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B1" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>61.3</v>
+      </c>
+      <c r="D3">
+        <v>68.3</v>
+      </c>
+      <c r="H3">
+        <v>28.7</v>
+      </c>
+      <c r="I3">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="M3">
+        <v>10.1</v>
+      </c>
+      <c r="N3">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="L1:P1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/results/training.xlsx
+++ b/results/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\projects\RF_DCOPF\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDDD66A-F882-4540-A65B-0192E8099568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3620D76-4D32-4A41-8034-CB6EBD5A6685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -471,24 +471,6 @@
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="C3">
-        <v>61.3</v>
-      </c>
-      <c r="D3">
-        <v>68.3</v>
-      </c>
-      <c r="H3">
-        <v>28.7</v>
-      </c>
-      <c r="I3">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="M3">
-        <v>10.1</v>
-      </c>
-      <c r="N3">
-        <v>10.8</v>
-      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">

--- a/results/training.xlsx
+++ b/results/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\projects\RF_DCOPF\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3620D76-4D32-4A41-8034-CB6EBD5A6685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FD2C41-BB96-4787-856F-6FC38E0700C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
   <si>
     <t>pglib_opf_case73_ieee_rts</t>
   </si>
@@ -73,6 +73,24 @@
   </si>
   <si>
     <t>mlp</t>
+  </si>
+  <si>
+    <t>62.92% ± 1.10%</t>
+  </si>
+  <si>
+    <t>27.94% ± 0.76%</t>
+  </si>
+  <si>
+    <t>10.56% ± 0.20%</t>
+  </si>
+  <si>
+    <t>56.10% ± 0.48%</t>
+  </si>
+  <si>
+    <t>25.62% ± 0.88%</t>
+  </si>
+  <si>
+    <t>8.82% ± 0.66%</t>
   </si>
 </sst>
 </file>
@@ -471,6 +489,24 @@
       <c r="A3" t="s">
         <v>0</v>
       </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">

--- a/results/training.xlsx
+++ b/results/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\projects\RF_DCOPF\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FD2C41-BB96-4787-856F-6FC38E0700C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB1355B-B598-4226-BE3B-CE5D2238A46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="85">
   <si>
     <t>pglib_opf_case73_ieee_rts</t>
   </si>
@@ -91,19 +91,220 @@
   </si>
   <si>
     <t>8.82% ± 0.66%</t>
+  </si>
+  <si>
+    <t>83.20% ± 0.36%</t>
+  </si>
+  <si>
+    <t>75.78% ± 1.09%</t>
+  </si>
+  <si>
+    <t>72.96% ± 0.94%</t>
+  </si>
+  <si>
+    <t>90.66% ± 0.89%</t>
+  </si>
+  <si>
+    <t>82.92% ± 0.62%</t>
+  </si>
+  <si>
+    <t>78.58% ± 0.93%</t>
+  </si>
+  <si>
+    <t>66.62% ± 1.19%</t>
+  </si>
+  <si>
+    <t>33.48% ± 1.22%</t>
+  </si>
+  <si>
+    <t>11.22% ± 0.59%</t>
+  </si>
+  <si>
+    <t>51.64% ± 1.11%</t>
+  </si>
+  <si>
+    <t>29.20% ± 0.36%</t>
+  </si>
+  <si>
+    <t>13.14% ± 0.88%</t>
+  </si>
+  <si>
+    <t>89.80% ± 0.53%</t>
+  </si>
+  <si>
+    <t>83.72% ± 0.63%</t>
+  </si>
+  <si>
+    <t>80.50% ± 1.05%</t>
+  </si>
+  <si>
+    <t>84.92% ± 0.54%</t>
+  </si>
+  <si>
+    <t>80.74% ± 0.27%</t>
+  </si>
+  <si>
+    <t>77.58% ± 1.85%</t>
+  </si>
+  <si>
+    <t>97.32% ± 0.41%</t>
+  </si>
+  <si>
+    <t>89.26% ± 0.48%</t>
+  </si>
+  <si>
+    <t>75.24% ± 1.13%</t>
+  </si>
+  <si>
+    <t>77.02% ± 1.15%</t>
+  </si>
+  <si>
+    <t>68.98% ± 1.13%</t>
+  </si>
+  <si>
+    <t>42.32% ± 1.32%</t>
+  </si>
+  <si>
+    <t>98.66% ± 0.26%</t>
+  </si>
+  <si>
+    <t>93.18% ± 0.34%</t>
+  </si>
+  <si>
+    <t>83.60% ± 1.10%</t>
+  </si>
+  <si>
+    <t>81.22% ± 0.97%</t>
+  </si>
+  <si>
+    <t>77.38% ± 0.63%</t>
+  </si>
+  <si>
+    <t>99.76% ± 0.15%</t>
+  </si>
+  <si>
+    <t>96.04% ± 0.39%</t>
+  </si>
+  <si>
+    <t>93.48% ± 0.94%</t>
+  </si>
+  <si>
+    <t>74.26% ± 0.83%</t>
+  </si>
+  <si>
+    <t>50.92% ± 1.63%</t>
+  </si>
+  <si>
+    <t>90.52% ± 0.38%</t>
+  </si>
+  <si>
+    <t>77.96% ± 0.92%</t>
+  </si>
+  <si>
+    <t>92.80% ± 0.32%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.80% ± 0.33% </t>
+  </si>
+  <si>
+    <t>85.96% ± 1.55%</t>
+  </si>
+  <si>
+    <t>83.42% ± 0.55%</t>
+  </si>
+  <si>
+    <t>60.50% ± 1.01%</t>
+  </si>
+  <si>
+    <t>49.82% ± 0.89%</t>
+  </si>
+  <si>
+    <t>72.22% ± 0.70%</t>
+  </si>
+  <si>
+    <t>83.44% ± 0.67%</t>
+  </si>
+  <si>
+    <t>96.26% ± 0.45%</t>
+  </si>
+  <si>
+    <t>72.36% ± 1.24%</t>
+  </si>
+  <si>
+    <t>66.78% ± 1.12%</t>
+  </si>
+  <si>
+    <t>48.26% ± 0.51%</t>
+  </si>
+  <si>
+    <t>99.86% ± 0.08%</t>
+  </si>
+  <si>
+    <t>97.64% ± 0.26%</t>
+  </si>
+  <si>
+    <t>95.52% ± 0.27%</t>
+  </si>
+  <si>
+    <t>100.00% ± 0.00%</t>
+  </si>
+  <si>
+    <t>46.04% ± 2.12%</t>
+  </si>
+  <si>
+    <t>3.24% ± 0.42%</t>
+  </si>
+  <si>
+    <t>0.12% ± 0.07%</t>
+  </si>
+  <si>
+    <t>99.26% ± 0.08%</t>
+  </si>
+  <si>
+    <t>71.08% ± 0.48%</t>
+  </si>
+  <si>
+    <t>42.64% ± 0.98%</t>
+  </si>
+  <si>
+    <t>97.14% ± 0.52%</t>
+  </si>
+  <si>
+    <t>82.04% ± 0.68%</t>
+  </si>
+  <si>
+    <t>40.54% ± 1.38%</t>
+  </si>
+  <si>
+    <t>23.40% ± 0.61%</t>
+  </si>
+  <si>
+    <t>10.88% ± 1.09%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF202020"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -126,9 +327,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -414,29 +617,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B1" s="2">
+      <c r="B1" s="4">
         <v>0.01</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2">
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4">
         <v>0.03</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2">
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4">
         <v>0.5</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
@@ -495,67 +701,265 @@
       <c r="C3" t="s">
         <v>16</v>
       </c>
+      <c r="D3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="G3" t="s">
         <v>20</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
       </c>
+      <c r="I3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="L3" t="s">
         <v>21</v>
       </c>
       <c r="M3" t="s">
         <v>18</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
+      <c r="B5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
+      <c r="B7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
+      <c r="B8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
+      <c r="E9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
+      <c r="E10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>7</v>
       </c>
+      <c r="E11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
+      <c r="E12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -565,5 +969,6 @@
     <mergeCell ref="L1:P1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/results/training.xlsx
+++ b/results/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\projects\RF_DCOPF\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB1355B-B598-4226-BE3B-CE5D2238A46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD2D56AB-D06D-449C-8D29-53DFF924316D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="137">
   <si>
     <t>pglib_opf_case73_ieee_rts</t>
   </si>
@@ -280,6 +280,162 @@
   </si>
   <si>
     <t>10.88% ± 1.09%</t>
+  </si>
+  <si>
+    <t>99.86% ± 0.12%</t>
+  </si>
+  <si>
+    <t>97.36% ± 0.19%</t>
+  </si>
+  <si>
+    <t>91.50% ± 0.51%</t>
+  </si>
+  <si>
+    <t>96.92% ± 0.45%</t>
+  </si>
+  <si>
+    <t>83.20% ± 0.58%</t>
+  </si>
+  <si>
+    <t>55.40% ± 1.13%</t>
+  </si>
+  <si>
+    <t>81.78% ± 0.40%</t>
+  </si>
+  <si>
+    <t>54.08% ± 1.83%</t>
+  </si>
+  <si>
+    <t>83.76% ± 1.33%</t>
+  </si>
+  <si>
+    <t>51.18% ± 12.60%</t>
+  </si>
+  <si>
+    <t>41.22% ± 1.52%</t>
+  </si>
+  <si>
+    <t>15.64% ± 1.49%</t>
+  </si>
+  <si>
+    <t>81.02% ± 4.48%</t>
+  </si>
+  <si>
+    <t>78.22% ± 0.96%</t>
+  </si>
+  <si>
+    <t>77.52% ± 1.66%</t>
+  </si>
+  <si>
+    <t>95.52% ± 0.66%</t>
+  </si>
+  <si>
+    <t>92.14% ± 1.41%</t>
+  </si>
+  <si>
+    <t>82.24% ± 1.24%</t>
+  </si>
+  <si>
+    <t>81.04% ± 2.35%</t>
+  </si>
+  <si>
+    <t>98.22% ± 0.25%</t>
+  </si>
+  <si>
+    <t>92.98% ± 0.84%</t>
+  </si>
+  <si>
+    <t>80.96% ± 0.85%</t>
+  </si>
+  <si>
+    <t>86.48% ± 2.16%</t>
+  </si>
+  <si>
+    <t>84.90% ± 1.25%</t>
+  </si>
+  <si>
+    <t>80.28% ± 2.63%</t>
+  </si>
+  <si>
+    <t>94.66% ± 0.62%</t>
+  </si>
+  <si>
+    <t>91.92% ± 1.48%</t>
+  </si>
+  <si>
+    <t>7.82% ± 0.75%</t>
+  </si>
+  <si>
+    <t>94.46% ± 0.94%</t>
+  </si>
+  <si>
+    <t>82.48% ± 1.18%</t>
+  </si>
+  <si>
+    <t>63.72% ± 0.63%</t>
+  </si>
+  <si>
+    <t>44.06% ± 1.37%</t>
+  </si>
+  <si>
+    <t>7.00% ± 2.15%</t>
+  </si>
+  <si>
+    <t>0.56% ± 0.36%</t>
+  </si>
+  <si>
+    <t>80.62% ± 0.95%</t>
+  </si>
+  <si>
+    <t>61.52% ± 3.00%</t>
+  </si>
+  <si>
+    <t>82.36% ± 0.57%</t>
+  </si>
+  <si>
+    <t>31.34% ± 1.06%</t>
+  </si>
+  <si>
+    <t>27.26% ± 5.63%</t>
+  </si>
+  <si>
+    <t>15.24% ± 3.81%</t>
+  </si>
+  <si>
+    <t>91.14% ± 0.50%</t>
+  </si>
+  <si>
+    <t>87.62% ± 0.82%</t>
+  </si>
+  <si>
+    <t>83.90% ± 0.70%</t>
+  </si>
+  <si>
+    <t>1.02% ± 0.26%</t>
+  </si>
+  <si>
+    <t>46.92% ± 1.63%</t>
+  </si>
+  <si>
+    <t>97.04% ± 0.16%</t>
+  </si>
+  <si>
+    <t>94.18% ± 0.34%</t>
+  </si>
+  <si>
+    <t>8.02% ± 0.74%</t>
+  </si>
+  <si>
+    <t>0.54% ± 0.19%</t>
+  </si>
+  <si>
+    <t>73.80% ± 1.11%</t>
+  </si>
+  <si>
+    <t>45.32% ± 0.47%</t>
+  </si>
+  <si>
+    <t>82.36% ± 0.61%</t>
   </si>
 </sst>
 </file>
@@ -619,6 +775,18 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -707,6 +875,9 @@
       <c r="E3" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="G3" t="s">
         <v>20</v>
       </c>
@@ -719,6 +890,9 @@
       <c r="J3" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="K3" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="L3" t="s">
         <v>21</v>
       </c>
@@ -730,6 +904,9 @@
       </c>
       <c r="O3" s="2" t="s">
         <v>33</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
@@ -748,6 +925,9 @@
       <c r="E4" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="F4" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="G4" s="3" t="s">
         <v>23</v>
       </c>
@@ -760,6 +940,9 @@
       <c r="J4" s="3" t="s">
         <v>38</v>
       </c>
+      <c r="K4" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="L4" s="3" t="s">
         <v>24</v>
       </c>
@@ -771,6 +954,9 @@
       </c>
       <c r="O4" s="3" t="s">
         <v>39</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
@@ -783,26 +969,44 @@
       <c r="C5" s="2" t="s">
         <v>46</v>
       </c>
+      <c r="D5" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="E5" s="3" t="s">
         <v>66</v>
       </c>
+      <c r="F5" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="G5" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="I5" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="J5" s="3" t="s">
         <v>65</v>
       </c>
+      <c r="K5" s="2" t="s">
+        <v>101</v>
+      </c>
       <c r="L5" s="2" t="s">
         <v>42</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="N5" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="O5" s="3" t="s">
         <v>64</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
@@ -815,26 +1019,44 @@
       <c r="C6" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="D6" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="E6" s="3" t="s">
         <v>67</v>
       </c>
+      <c r="F6" s="2" t="s">
+        <v>103</v>
+      </c>
       <c r="G6" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="I6" s="3" t="s">
+        <v>114</v>
+      </c>
       <c r="J6" s="3" t="s">
         <v>68</v>
       </c>
+      <c r="K6" s="2" t="s">
+        <v>103</v>
+      </c>
       <c r="L6" s="2" t="s">
         <v>45</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="N6" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="O6" s="3" t="s">
         <v>69</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -847,26 +1069,44 @@
       <c r="C7" s="3" t="s">
         <v>58</v>
       </c>
+      <c r="D7" s="3" t="s">
+        <v>125</v>
+      </c>
       <c r="E7" s="3" t="s">
         <v>61</v>
       </c>
+      <c r="F7" s="2" t="s">
+        <v>107</v>
+      </c>
       <c r="G7" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>59</v>
       </c>
+      <c r="I7" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="J7" s="3" t="s">
         <v>62</v>
       </c>
+      <c r="K7" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="L7" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>60</v>
       </c>
+      <c r="N7" s="3" t="s">
+        <v>127</v>
+      </c>
       <c r="O7" s="3" t="s">
         <v>63</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
@@ -876,33 +1116,96 @@
       <c r="B8" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="C8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="E8" s="3" t="s">
         <v>70</v>
       </c>
+      <c r="F8" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="G8" s="2" t="s">
         <v>52</v>
       </c>
+      <c r="H8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="J8" s="3" t="s">
         <v>71</v>
       </c>
+      <c r="K8" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="L8" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="M8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="O8" s="3" t="s">
         <v>72</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
+      <c r="B9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="E9" s="3" t="s">
         <v>73</v>
       </c>
+      <c r="F9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="J9" s="3" t="s">
         <v>73</v>
       </c>
+      <c r="K9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="O9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>73</v>
       </c>
     </row>
@@ -910,56 +1213,149 @@
       <c r="A10" t="s">
         <v>6</v>
       </c>
+      <c r="B10" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="E10" s="3" t="s">
         <v>74</v>
       </c>
+      <c r="F10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>112</v>
+      </c>
       <c r="J10" s="3" t="s">
         <v>75</v>
       </c>
+      <c r="K10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="O10" s="3" t="s">
         <v>76</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>7</v>
       </c>
+      <c r="B11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="E11" s="3" t="s">
         <v>77</v>
       </c>
+      <c r="F11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="J11" s="3" t="s">
         <v>78</v>
       </c>
+      <c r="K11" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="O11" s="3" t="s">
         <v>79</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
+      <c r="B12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="E12" s="3" t="s">
         <v>73</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>80</v>
       </c>
+      <c r="K12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="O12" s="3" t="s">
         <v>81</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
+      <c r="C13" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="E13" s="3" t="s">
         <v>82</v>
       </c>
+      <c r="F13" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="J13" s="3" t="s">
         <v>83</v>
       </c>
+      <c r="K13" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="O13" s="3" t="s">
         <v>84</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/results/training.xlsx
+++ b/results/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\projects\RF_DCOPF\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD2D56AB-D06D-449C-8D29-53DFF924316D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F94409-9042-4546-9348-4BF59F9E83A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="142">
   <si>
     <t>pglib_opf_case73_ieee_rts</t>
   </si>
@@ -436,6 +436,21 @@
   </si>
   <si>
     <t>82.36% ± 0.61%</t>
+  </si>
+  <si>
+    <t>69.60% ± 1.50%</t>
+  </si>
+  <si>
+    <t>37.42% ± 0.98%</t>
+  </si>
+  <si>
+    <t>24.18% ± 2.24%</t>
+  </si>
+  <si>
+    <t>3.76% ± 0.49%</t>
+  </si>
+  <si>
+    <t>14.62% ± 1.00%</t>
   </si>
 </sst>
 </file>
@@ -1336,6 +1351,9 @@
       <c r="A13" t="s">
         <v>9</v>
       </c>
+      <c r="B13" s="2" t="s">
+        <v>137</v>
+      </c>
       <c r="C13" s="3" t="s">
         <v>93</v>
       </c>
@@ -1345,11 +1363,23 @@
       <c r="F13" s="2" t="s">
         <v>122</v>
       </c>
+      <c r="G13" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="J13" s="3" t="s">
         <v>83</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>123</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="O13" s="3" t="s">
         <v>84</v>

--- a/results/training.xlsx
+++ b/results/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\projects\RF_DCOPF\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F94409-9042-4546-9348-4BF59F9E83A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A250DE-282F-46D2-B7A3-FECD927BCABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="training_performance_percentage" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="151">
   <si>
     <t>pglib_opf_case73_ieee_rts</t>
   </si>
@@ -451,6 +451,33 @@
   </si>
   <si>
     <t>14.62% ± 1.00%</t>
+  </si>
+  <si>
+    <t>3.08% ± 0.33%</t>
+  </si>
+  <si>
+    <t>14.46% ± 0.69%</t>
+  </si>
+  <si>
+    <t>58.82% ± 1.10%</t>
+  </si>
+  <si>
+    <t>17.80% ± 0.93%</t>
+  </si>
+  <si>
+    <t>81.18% ± 1.43%</t>
+  </si>
+  <si>
+    <t>45.96% ± 0.81%</t>
+  </si>
+  <si>
+    <t>84.58% ± 0.47%</t>
+  </si>
+  <si>
+    <t>54.48% ± 0.71%</t>
+  </si>
+  <si>
+    <t>82.56% ± 0.64%</t>
   </si>
 </sst>
 </file>
@@ -1234,6 +1261,9 @@
       <c r="C10" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="D10" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="E10" s="3" t="s">
         <v>74</v>
       </c>
@@ -1246,6 +1276,9 @@
       <c r="H10" s="2" t="s">
         <v>112</v>
       </c>
+      <c r="I10" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="J10" s="3" t="s">
         <v>75</v>
       </c>
@@ -1257,6 +1290,9 @@
       </c>
       <c r="M10" s="2" t="s">
         <v>128</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>76</v>
@@ -1275,6 +1311,9 @@
       <c r="C11" s="2" t="s">
         <v>77</v>
       </c>
+      <c r="D11" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="E11" s="3" t="s">
         <v>77</v>
       </c>
@@ -1287,6 +1326,9 @@
       <c r="H11" s="2" t="s">
         <v>89</v>
       </c>
+      <c r="I11" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="J11" s="3" t="s">
         <v>78</v>
       </c>
@@ -1298,6 +1340,9 @@
       </c>
       <c r="M11" s="2" t="s">
         <v>90</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>149</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>79</v>
@@ -1316,6 +1361,9 @@
       <c r="C12" s="3" t="s">
         <v>73</v>
       </c>
+      <c r="D12" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E12" s="3" t="s">
         <v>73</v>
       </c>
@@ -1328,6 +1376,9 @@
       <c r="H12" s="3" t="s">
         <v>88</v>
       </c>
+      <c r="I12" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="J12" s="3" t="s">
         <v>80</v>
       </c>
@@ -1339,6 +1390,9 @@
       </c>
       <c r="M12" s="3" t="s">
         <v>91</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>150</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>81</v>
@@ -1357,6 +1411,9 @@
       <c r="C13" s="3" t="s">
         <v>93</v>
       </c>
+      <c r="D13" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="E13" s="3" t="s">
         <v>82</v>
       </c>
@@ -1369,6 +1426,9 @@
       <c r="H13" s="2" t="s">
         <v>138</v>
       </c>
+      <c r="I13" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="J13" s="3" t="s">
         <v>83</v>
       </c>
@@ -1380,6 +1440,9 @@
       </c>
       <c r="M13" s="2" t="s">
         <v>141</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="O13" s="3" t="s">
         <v>84</v>

--- a/results/training.xlsx
+++ b/results/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\projects\RF_DCOPF\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A250DE-282F-46D2-B7A3-FECD927BCABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2CE530-4151-41B8-B48C-F106E07C3B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="training_performance_percentage" sheetId="1" r:id="rId1"/>
